--- a/circunscripcion-c3/datos/Calendario y coordinación C3.xlsx
+++ b/circunscripcion-c3/datos/Calendario y coordinación C3.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendario" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Morena" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Responsables" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -453,13 +454,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -483,6 +486,16 @@
           <t>Etapa que abre</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Carril</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -495,6 +508,12 @@
       </c>
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Proceso electoral</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -507,6 +526,12 @@
       </c>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Proceso electoral</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -519,14 +544,20 @@
       </c>
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Proceso electoral</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46391</v>
+        <v>46387</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Inicio de precampañas</t>
+          <t>Publicación de registros aprobados de coordinaciones federales</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -534,19 +565,25 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Precampañas</t>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Morena</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>A más tardar en esta fecha, en la página oficial de Morena</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46430</v>
+        <v>46391</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Fin de precampañas</t>
+          <t>Inicio de precampañas</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -556,17 +593,23 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Intercampaña</t>
-        </is>
-      </c>
+          <t>Precampañas</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Proceso electoral</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46481</v>
+        <v>46430</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Inicio de campañas</t>
+          <t>Fin de precampañas</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -576,17 +619,23 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Campañas</t>
-        </is>
-      </c>
+          <t>Intercampaña</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Proceso electoral</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46540</v>
+        <v>46481</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Fin de campañas</t>
+          <t>Inicio de campañas</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -596,17 +645,23 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Veda</t>
-        </is>
-      </c>
+          <t>Campañas</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Proceso electoral</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46544</v>
+        <v>46540</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Jornada electoral</t>
+          <t>Fin de campañas</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -616,33 +671,77 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Cómputos</t>
-        </is>
-      </c>
+          <t>Veda</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Proceso electoral</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46547</v>
+        <v>46544</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cómputos distritales</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
+          <t>Jornada electoral</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Cómputos</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Proceso electoral</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46551</v>
+        <v>46547</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Cómputo plurinominal</t>
+          <t>Cómputos distritales</t>
         </is>
       </c>
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Proceso electoral</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46551</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Cómputo plurinominal</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Proceso electoral</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1229,7 +1328,425 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Cargo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Partido</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Rocío Nahle García</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Gobernadora</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Morena</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>wiki:Rocío Nahle García</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Salomón Jara Cruz</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Gobernador</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Morena</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>wiki:Salomón Jara Cruz</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Eduardo Ramírez Aguilar</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Gobernador</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Morena</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>wiki:Eduardo Ramírez Aguilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Javier May Rodríguez</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Gobernador</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Morena</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>wiki:Javier May Rodríguez</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Layda Sansores San Román</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Gobernadora</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Morena</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>wiki:Layda Sansores</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Joaquín Díaz Mena</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Gobernador</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Morena</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>wiki:Joaquín Díaz Mena</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Mara Lezama Espinosa</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Gobernadora</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Morena</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>wiki:Mara Lezama</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Pablo Gutiérrez Lazarus</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Coordinador estatal de Morena</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Morena</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>wiki:Pablo Gutiérrez Lazarus</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Eugenio “Gino” Segura Vázquez</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Coordinador estatal de Morena</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Morena</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>wiki:Eugenio Segura Vázquez</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Rafael Marín Mollinedo</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Aspirante</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Morena</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>wiki:Rafael Marín Mollinedo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Eliseo Fernández Montúfar</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Aspirante</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>MC</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>wiki:Eliseo Fernández Montúfar</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Biby Rabelo</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Presidenta municipal de Campeche</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>MC</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>wiki:Biby Rabelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Ana Paty Peralta</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Presidenta municipal de Benito Juárez</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>PVEM</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>wiki:Ana Paty Peralta</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Ulloa</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Director general de Birmex</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1266,6 +1783,20 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t>Carril: Proceso electoral o Morena. Las fechas de Morena aparecen en su propia línea y no cambian el contador principal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Personas: gobernadores, coordinadores y actores de las notas. En Foto puedes poner un enlace a una imagen, el nombre de un archivo subido a la carpeta circunscripcion-c3/fotos, o wiki: seguido del título del artículo de Wikipedia en español. Si queda vacío se muestran las iniciales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
           <t>No cambies los títulos de las columnas ni los nombres de las hojas.</t>
         </is>
       </c>

--- a/circunscripcion-c3/datos/Calendario y coordinación C3.xlsx
+++ b/circunscripcion-c3/datos/Calendario y coordinación C3.xlsx
@@ -1469,7 +1469,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>wiki:Javier May Rodríguez</t>
+          <t>wiki:Javier May Rodríguez|javier-may.jpg</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>wiki:Mara Lezama</t>
+          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Mara_Lezama_Gobernadora_de_Quintana_Roo.jpg?width=250|wiki:Mara Lezama|mara-lezama.jpg</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>wiki:Pablo Gutiérrez Lazarus</t>
+          <t>pablo-gutierrez-lazarus.jpg|wiki:Pablo Gutiérrez Lazarus</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>wiki:Eugenio Segura Vázquez</t>
+          <t>gino-segura.jpg|wiki:Eugenio Segura Vázquez</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Personas: gobernadores, coordinadores y actores de las notas. En Foto puedes poner un enlace a una imagen, el nombre de un archivo subido a la carpeta circunscripcion-c3/fotos, o wiki: seguido del título del artículo de Wikipedia en español. Si queda vacío se muestran las iniciales.</t>
+          <t>Personas: gobernadores, coordinadores y actores de las notas. En Foto puedes poner un enlace a una imagen, el nombre de un archivo subido a la carpeta circunscripcion-c3/fotos, o wiki: seguido del título del artículo de Wikipedia en español. Puedes poner varias opciones separadas por | y se usa la primera que cargue. Si ninguna carga se muestran las iniciales.</t>
         </is>
       </c>
     </row>
